--- a/www/flightdata/xlsx/eoss-305.xlsx
+++ b/www/flightdata/xlsx/eoss-305.xlsx
@@ -3429,7 +3429,7 @@
         <v>27325.62</v>
       </c>
       <c r="I2">
-        <v>594</v>
+        <v>435</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
